--- a/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/S1#111#DIGITALMINDSSRLXX/digitalminds/XilemaFSE/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\stefano\src\it-fse-accreditamento\GATEWAY\S1#111#DIGITALMINDSSRLXX\digitalminds\XilemaFSE\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE558A-E04E-4DA5-A720-507FFD25082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62330874-5235-4080-8E17-F07B994A94BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Summary!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="258">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -350,6 +350,9 @@
     <t>RSA</t>
   </si>
   <si>
+    <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
+  </si>
+  <si>
     <t>CERT_VAC</t>
   </si>
   <si>
@@ -408,6 +411,9 @@
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RAD_KO</t>
   </si>
   <si>
+    <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
+  </si>
+  <si>
     <t>Per questo caso di test è richiesta la sola descrizione del comportamento a fronte di un timeout, da inserire nelle colonne relative a:
 "ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
   </si>
@@ -418,6 +424,9 @@
     <t>VALIDAZIONE_RAD_TIMEOUT</t>
   </si>
   <si>
+    <t>VALIDAZIONE_RSA_TIMEOUT</t>
+  </si>
+  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT6_KO</t>
   </si>
   <si>
@@ -530,7 +539,133 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT6_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT8_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
     <t>RAP</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT24</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT25</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT26_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RAD_CT24_KO</t>
@@ -540,6 +675,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 24" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT27_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT25</t>
   </si>
   <si>
@@ -561,6 +703,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
+    <t>VALIDAZIONE_CDA2_RSA_CT28_KO</t>
+  </si>
+  <si>
+    <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
     <t>TPI</t>
   </si>
   <si>
@@ -819,6 +968,88 @@
   </si>
   <si>
     <t>Il software non gestisce la storia clinica e le allegie</t>
+  </si>
+  <si>
+    <t>Il campo effectivetime/low ha sempre un valore di default, se non è presente la data perché non è disponbile (es. il paziente non ricorda) allora è presente il valore @nullFlavor = “UNK”.</t>
+  </si>
+  <si>
+    <t>l campo effectivetime/low ha sempre un valore di default, se non è presente la data perché non è disponbile (es. il paziente non ricorda) allora è presente il valore @nullFlavor = “UNK”.</t>
+  </si>
+  <si>
+    <t>2026-03-26T15:54:11.727Z</t>
+  </si>
+  <si>
+    <t>21c7a17ac94f807c7a860e7d5f085549</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.df44d22697c53c60bf527e12902370d4c4d03b601c343f4f0fa4bcf8992b3288.97862f7802^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-26T16:05:32.288Z</t>
+  </si>
+  <si>
+    <t>74483ee5a77153b5be62b06e5655d826</t>
+  </si>
+  <si>
+    <t>UNKNOWN_WORKFLOW_ID</t>
+  </si>
+  <si>
+    <t>Viene segnalato un errore di token non valido all'utente</t>
+  </si>
+  <si>
+    <t>2026-03-26T16:10:31.272Z</t>
+  </si>
+  <si>
+    <t>c57d5241dc918320f9326e90f0239292</t>
+  </si>
+  <si>
+    <t>È stato segnalato un errore di connessione al gateway, causato da un valore errato del campo action_id. Si richiede di notificare il problema all’amministratore di sistema per consentire le opportune verifiche.
+L’operatore incaricato provvederà a integrare nel software i parametri necessari per la corretta generazione dei token JWT e, una volta effettuata la correzione, procederà con la validazione e il reinvio dei referti.</t>
+  </si>
+  <si>
+    <t>Viene segnalato un errore di timeout, l'errore indica che il sistema non è riuscito a completare l'elaborazione entro il tempo limite previsto. L'utente compilatore è invitato a riprovare l'operazione in un momento successivo,</t>
+  </si>
+  <si>
+    <t>Il software rende il codice fiscale scritto sempre in maiuscolo indipendentemente da come è stato compilato dall'utente utilizzatore</t>
+  </si>
+  <si>
+    <t>Il software verifica che il comune di residenza sia compilato prima della generazione e dell'invio del referto</t>
+  </si>
+  <si>
+    <t>Il software verifica che il nome del paziente sia compilato prima della generazione e dell'invio del referto</t>
+  </si>
+  <si>
+    <t>2026-03-26T16:25:17.204Z</t>
+  </si>
+  <si>
+    <t>8f69d6c289e26160e16acb2e07b20bf7</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.1.e6def8a21b81288abc41ccb6a6cf1c3ad9e9d28ccedea5a3025da267183fb403.24379861cc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Errore di sintassi. ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element 'priorityCode'. One of '{\"urn:hl7-org:v3\":realmCode, \"urn:hl7-org:v3\":typeId, \"urn:hl7-org:v3\":templateId, \"urn:hl7-org:v3\":id}' is expected</t>
+  </si>
+  <si>
+    <t>Il controllo del file xml viene eseguito prima dell'invio</t>
+  </si>
+  <si>
+    <t>Il software verifica la validità e la presenza del valore prima della generazione e dell'invio del referto</t>
+  </si>
+  <si>
+    <t>Il software verifica la validità e la presenza dei valori prima della generazione e dell'invio del referto</t>
+  </si>
+  <si>
+    <t>In mancanza della compilazione del quesito diagnostico, non viene inclusa l'intera sezione linicalDocument/component/structuredBody/component/section[@ID=Quesito_Diagnostico]</t>
+  </si>
+  <si>
+    <t>Il software non gestisce la storia clinica né l'anamnesi familiare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il software non gestisce la storia clinica </t>
+  </si>
+  <si>
+    <t>Il software impedisce che arrivi un valore differente da quelli accettati</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1543,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1480,6 +1711,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2919,7 +3153,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W535"/>
+  <dimension ref="A1:W558"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.453125" customWidth="1"/>
@@ -2990,7 +3224,7 @@
       </c>
       <c r="B3" s="60"/>
       <c r="C3" s="65" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="D3" s="57"/>
       <c r="F3" s="6"/>
@@ -3016,7 +3250,7 @@
       <c r="A4" s="61"/>
       <c r="B4" s="62"/>
       <c r="C4" s="65" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="4"/>
@@ -3043,7 +3277,7 @@
       <c r="A5" s="63"/>
       <c r="B5" s="64"/>
       <c r="C5" s="65" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="D5" s="57"/>
       <c r="F5" s="6"/>
@@ -3222,37 +3456,37 @@
         <v>46098</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="I10" s="45"/>
       <c r="J10" s="46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
       <c r="M10" s="46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="P10" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q10" s="47" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="R10" s="47" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="S10" s="47" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="T10" s="47"/>
       <c r="U10" s="48"/>
@@ -3261,68 +3495,70 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="41">
+    <row r="11" spans="1:23" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="31">
+        <v>32</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="R11" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="S11" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="T11" s="33"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="50" customFormat="1" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="41">
         <v>39</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="44">
-        <v>46098</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>158</v>
-      </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="N11" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="O11" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="P11" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q11" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="R11" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="S11" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="T11" s="47"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" s="50" customFormat="1" ht="102" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="41">
-        <v>47</v>
       </c>
       <c r="B12" s="41" t="s">
         <v>43</v>
@@ -3331,259 +3567,295 @@
         <v>50</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="44">
         <v>46098</v>
       </c>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
+      <c r="G12" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>201</v>
+      </c>
       <c r="I12" s="45"/>
       <c r="J12" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
       <c r="M12" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q12" s="47" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="R12" s="47" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="S12" s="47" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="T12" s="47"/>
-      <c r="U12" s="48" t="s">
-        <v>59</v>
-      </c>
+      <c r="U12" s="48"/>
       <c r="V12" s="49"/>
       <c r="W12" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="50" customFormat="1" ht="189" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="41">
-        <v>76</v>
-      </c>
-      <c r="B13" s="41" t="s">
+    <row r="13" spans="1:23" ht="247" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="31">
+        <v>40</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="R13" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="S13" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="T13" s="33"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="50" customFormat="1" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="41">
+        <v>47</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D14" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="44">
+        <v>46098</v>
+      </c>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="44">
-        <v>46098</v>
-      </c>
-      <c r="G13" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="J13" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="P13" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q13" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="R13" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="S13" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="T13" s="47"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="47" t="s">
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="P14" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q14" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="R14" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="S14" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="T14" s="47"/>
+      <c r="U14" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="V14" s="49"/>
+      <c r="W14" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31">
-        <v>78</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="32">
-        <v>46101</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="O14" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="P14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q14" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="R14" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="S14" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="T14" s="33"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="32"/>
+        <v>60</v>
+      </c>
+      <c r="F15" s="32">
+        <v>46107</v>
+      </c>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>108</v>
-      </c>
+      <c r="I15" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="33"/>
       <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
+      <c r="M15" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="P15" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="R15" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" s="51" t="s">
+        <v>243</v>
+      </c>
       <c r="T15" s="33"/>
-      <c r="U15" s="34"/>
+      <c r="U15" s="34" t="s">
+        <v>61</v>
+      </c>
       <c r="V15" s="35"/>
       <c r="W15" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="31">
-        <v>80</v>
-      </c>
-      <c r="B16" s="31" t="s">
+    <row r="16" spans="1:23" s="50" customFormat="1" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="41">
+        <v>76</v>
+      </c>
+      <c r="B16" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="K16" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="33" t="s">
+      <c r="D16" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="44">
+        <v>46098</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="P16" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q16" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="R16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="S16" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="T16" s="47"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>43</v>
@@ -3592,29 +3864,49 @@
         <v>50</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="37"/>
+        <v>67</v>
+      </c>
+      <c r="F17" s="32">
+        <v>46101</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>214</v>
+      </c>
       <c r="J17" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="K17" s="51" t="s">
-        <v>111</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
+      <c r="M17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="R17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>216</v>
+      </c>
       <c r="T17" s="33"/>
       <c r="U17" s="34"/>
       <c r="V17" s="35"/>
@@ -3624,7 +3916,7 @@
     </row>
     <row r="18" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="31">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>43</v>
@@ -3633,20 +3925,20 @@
         <v>50</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="37"/>
       <c r="J18" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="51" t="s">
-        <v>111</v>
+        <v>193</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>151</v>
       </c>
       <c r="L18" s="33"/>
       <c r="M18" s="33"/>
@@ -3665,7 +3957,7 @@
     </row>
     <row r="19" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>43</v>
@@ -3674,20 +3966,20 @@
         <v>50</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="37"/>
-      <c r="J19" s="33" t="s">
-        <v>150</v>
+      <c r="J19" s="51" t="s">
+        <v>193</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="L19" s="33"/>
       <c r="M19" s="33"/>
@@ -3706,7 +3998,7 @@
     </row>
     <row r="20" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>43</v>
@@ -3715,49 +4007,29 @@
         <v>50</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="32">
-        <v>46107</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>178</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="37"/>
       <c r="J20" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="33"/>
+        <v>193</v>
+      </c>
+      <c r="K20" s="51" t="s">
+        <v>154</v>
+      </c>
       <c r="L20" s="33"/>
-      <c r="M20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="N20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="P20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q20" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="R20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="S20" s="51" t="s">
-        <v>182</v>
-      </c>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
       <c r="T20" s="33"/>
       <c r="U20" s="34"/>
       <c r="V20" s="35"/>
@@ -3767,7 +4039,7 @@
     </row>
     <row r="21" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="31">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>43</v>
@@ -3776,20 +4048,20 @@
         <v>50</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="37"/>
       <c r="J21" s="33" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="L21" s="33"/>
       <c r="M21" s="33"/>
@@ -3806,9 +4078,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="31">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>43</v>
@@ -3817,24 +4089,22 @@
         <v>50</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="51" t="s">
-        <v>150</v>
+      <c r="J22" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="L22" s="51" t="s">
-        <v>174</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="L22" s="33"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="33"/>
@@ -3851,7 +4121,7 @@
     </row>
     <row r="23" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="31">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>43</v>
@@ -3860,31 +4130,49 @@
         <v>50</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="L23" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
+        <v>79</v>
+      </c>
+      <c r="F23" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="J23" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="N23" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="O23" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="P23" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q23" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="R23" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="S23" s="51" t="s">
+        <v>225</v>
+      </c>
       <c r="T23" s="33"/>
       <c r="U23" s="34"/>
       <c r="V23" s="35"/>
@@ -3894,7 +4182,7 @@
     </row>
     <row r="24" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>43</v>
@@ -3903,24 +4191,22 @@
         <v>50</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="37"/>
-      <c r="J24" s="51" t="s">
-        <v>150</v>
+      <c r="J24" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="L24" s="51" t="s">
-        <v>176</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="L24" s="33"/>
       <c r="M24" s="33"/>
       <c r="N24" s="33"/>
       <c r="O24" s="33"/>
@@ -3935,9 +4221,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>43</v>
@@ -3946,23 +4232,23 @@
         <v>50</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="37"/>
       <c r="J25" s="51" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="L25" s="51" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="M25" s="33"/>
       <c r="N25" s="33"/>
@@ -3980,7 +4266,7 @@
     </row>
     <row r="26" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>43</v>
@@ -3989,23 +4275,23 @@
         <v>50</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="37"/>
-      <c r="J26" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="K26" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="L26" s="52" t="s">
-        <v>177</v>
+      <c r="J26" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="51" t="s">
+        <v>218</v>
       </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33"/>
@@ -4023,7 +4309,7 @@
     </row>
     <row r="27" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>43</v>
@@ -4032,22 +4318,24 @@
         <v>50</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="37"/>
-      <c r="J27" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="K27" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="L27" s="33"/>
+      <c r="J27" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="51" t="s">
+        <v>219</v>
+      </c>
       <c r="M27" s="33"/>
       <c r="N27" s="33"/>
       <c r="O27" s="33"/>
@@ -4064,7 +4352,7 @@
     </row>
     <row r="28" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>43</v>
@@ -4073,22 +4361,24 @@
         <v>50</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
       <c r="I28" s="37"/>
       <c r="J28" s="51" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="L28" s="33"/>
+        <v>156</v>
+      </c>
+      <c r="L28" s="51" t="s">
+        <v>218</v>
+      </c>
       <c r="M28" s="33"/>
       <c r="N28" s="33"/>
       <c r="O28" s="33"/>
@@ -4103,9 +4393,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31">
-        <v>462</v>
+        <v>91</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>43</v>
@@ -4114,39 +4404,41 @@
         <v>50</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="K29" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="L29" s="31"/>
+        <v>91</v>
+      </c>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="L29" s="52" t="s">
+        <v>220</v>
+      </c>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
-      <c r="O29" s="31"/>
+      <c r="O29" s="33"/>
       <c r="P29" s="33"/>
       <c r="Q29" s="33"/>
       <c r="R29" s="33"/>
-      <c r="S29" s="31"/>
+      <c r="S29" s="33"/>
       <c r="T29" s="33"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31" t="s">
+      <c r="U29" s="34"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31">
-        <v>471</v>
+        <v>92</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>43</v>
@@ -4155,27 +4447,21 @@
         <v>50</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="32">
-        <v>46107</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="K30" s="33"/>
+        <v>93</v>
+      </c>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="K30" s="53" t="s">
+        <v>154</v>
+      </c>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
@@ -4188,12 +4474,12 @@
       <c r="U30" s="34"/>
       <c r="V30" s="35"/>
       <c r="W30" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31">
-        <v>472</v>
+        <v>93</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>43</v>
@@ -4202,24 +4488,22 @@
         <v>50</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
       <c r="I31" s="37"/>
-      <c r="J31" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="K31" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="L31" s="33" t="s">
-        <v>187</v>
-      </c>
+      <c r="J31" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="L31" s="33"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
       <c r="O31" s="33"/>
@@ -4231,37 +4515,37 @@
       <c r="U31" s="34"/>
       <c r="V31" s="35"/>
       <c r="W31" s="33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
-        <v>474</v>
+        <v>152</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
       <c r="I32" s="37"/>
       <c r="J32" s="33" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="L32" s="33" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
@@ -4277,467 +4561,1012 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="9"/>
-    </row>
-    <row r="34" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="9"/>
-    </row>
-    <row r="35" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="9"/>
-    </row>
-    <row r="36" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="9"/>
-    </row>
-    <row r="37" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="9"/>
-    </row>
-    <row r="38" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="9"/>
-    </row>
-    <row r="39" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="9"/>
-    </row>
-    <row r="40" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="9"/>
-    </row>
-    <row r="41" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="9"/>
-    </row>
-    <row r="42" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="9"/>
-    </row>
-    <row r="43" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="2"/>
-      <c r="W43" s="9"/>
-    </row>
-    <row r="44" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="2"/>
-      <c r="W44" s="9"/>
-    </row>
-    <row r="45" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="9"/>
-    </row>
-    <row r="46" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="9"/>
-    </row>
-    <row r="47" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="9"/>
-    </row>
-    <row r="48" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="9"/>
-    </row>
-    <row r="49" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="9"/>
-    </row>
-    <row r="50" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="9"/>
-    </row>
-    <row r="51" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="9"/>
-    </row>
-    <row r="52" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="9"/>
-    </row>
-    <row r="53" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="7"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="9"/>
-    </row>
-    <row r="54" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="9"/>
-    </row>
-    <row r="55" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="8"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="9"/>
-    </row>
-    <row r="56" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="31">
+        <v>154</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K33" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="31">
+        <v>155</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K34" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="31">
+        <v>156</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="31">
+        <v>159</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="J36" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="33"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="O36" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="P36" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q36" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="R36" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="S36" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="T36" s="33"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="31">
+        <v>160</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K37" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="L37" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="31">
+        <v>161</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K38" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L38" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="34"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="31">
+        <v>162</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K39" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="31">
+        <v>163</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K40" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="L40" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="M40" s="33"/>
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="34"/>
+      <c r="V40" s="35"/>
+      <c r="W40" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="31">
+        <v>164</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="K41" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L41" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="34"/>
+      <c r="V41" s="35"/>
+      <c r="W41" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="31">
+        <v>165</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="L42" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="31">
+        <v>166</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="K43" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L43" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="M43" s="33"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="34"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="31">
+        <v>167</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K44" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="L44" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" s="33"/>
+      <c r="N44" s="33"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="35"/>
+      <c r="W44" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="31">
+        <v>168</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K45" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="34"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="31">
+        <v>169</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K46" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="L46" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="34"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="31">
+        <v>448</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="34"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="31">
+        <v>449</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K48" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="L48" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="34"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="31">
+        <v>461</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K49" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="L49" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="31">
+        <v>462</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K50" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L50" s="31"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
+      <c r="S50" s="31"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="31"/>
+      <c r="V50" s="31"/>
+      <c r="W50" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="31">
+        <v>468</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K51" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="L51" s="31"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="31">
+        <v>471</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F52" s="32">
+        <v>46107</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="J52" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="33"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="33"/>
+      <c r="T52" s="33"/>
+      <c r="U52" s="34"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="31">
+        <v>472</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K53" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="L53" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="M53" s="33"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="33"/>
+      <c r="T53" s="33"/>
+      <c r="U53" s="34"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="31">
+        <v>474</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L54" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
+      <c r="S54" s="33"/>
+      <c r="T54" s="33"/>
+      <c r="U54" s="34"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="31">
+        <v>475</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="37"/>
+      <c r="J55" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K55" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L55" s="33"/>
+      <c r="M55" s="33"/>
+      <c r="N55" s="33"/>
+      <c r="O55" s="33"/>
+      <c r="P55" s="33"/>
+      <c r="Q55" s="33"/>
+      <c r="R55" s="33"/>
+      <c r="S55" s="33"/>
+      <c r="T55" s="33"/>
+      <c r="U55" s="34"/>
+      <c r="V55" s="35"/>
+      <c r="W55" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -4757,7 +5586,7 @@
       <c r="V56" s="2"/>
       <c r="W56" s="9"/>
     </row>
-    <row r="57" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -4777,7 +5606,7 @@
       <c r="V57" s="2"/>
       <c r="W57" s="9"/>
     </row>
-    <row r="58" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -4797,7 +5626,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="9"/>
     </row>
-    <row r="59" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -4817,7 +5646,7 @@
       <c r="V59" s="2"/>
       <c r="W59" s="9"/>
     </row>
-    <row r="60" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -4837,7 +5666,7 @@
       <c r="V60" s="2"/>
       <c r="W60" s="9"/>
     </row>
-    <row r="61" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -4857,7 +5686,7 @@
       <c r="V61" s="2"/>
       <c r="W61" s="9"/>
     </row>
-    <row r="62" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -4877,7 +5706,7 @@
       <c r="V62" s="2"/>
       <c r="W62" s="9"/>
     </row>
-    <row r="63" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -4897,7 +5726,7 @@
       <c r="V63" s="2"/>
       <c r="W63" s="9"/>
     </row>
-    <row r="64" spans="6:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -5998,81 +6827,472 @@
       <c r="W118" s="9"/>
     </row>
     <row r="119" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W119" s="7"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7"/>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+      <c r="U119" s="8"/>
+      <c r="V119" s="2"/>
+      <c r="W119" s="9"/>
     </row>
     <row r="120" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W120" s="7"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="7"/>
+      <c r="K120" s="7"/>
+      <c r="L120" s="7"/>
+      <c r="M120" s="7"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="7"/>
+      <c r="P120" s="7"/>
+      <c r="Q120" s="7"/>
+      <c r="R120" s="7"/>
+      <c r="S120" s="7"/>
+      <c r="T120" s="7"/>
+      <c r="U120" s="8"/>
+      <c r="V120" s="2"/>
+      <c r="W120" s="9"/>
     </row>
     <row r="121" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W121" s="7"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7"/>
+      <c r="M121" s="7"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="7"/>
+      <c r="P121" s="7"/>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="7"/>
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+      <c r="U121" s="8"/>
+      <c r="V121" s="2"/>
+      <c r="W121" s="9"/>
     </row>
     <row r="122" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W122" s="7"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="7"/>
+      <c r="K122" s="7"/>
+      <c r="L122" s="7"/>
+      <c r="M122" s="7"/>
+      <c r="N122" s="7"/>
+      <c r="O122" s="7"/>
+      <c r="P122" s="7"/>
+      <c r="Q122" s="7"/>
+      <c r="R122" s="7"/>
+      <c r="S122" s="7"/>
+      <c r="T122" s="7"/>
+      <c r="U122" s="8"/>
+      <c r="V122" s="2"/>
+      <c r="W122" s="9"/>
     </row>
     <row r="123" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W123" s="7"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="6"/>
+      <c r="H123" s="6"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="7"/>
+      <c r="K123" s="7"/>
+      <c r="L123" s="7"/>
+      <c r="M123" s="7"/>
+      <c r="N123" s="7"/>
+      <c r="O123" s="7"/>
+      <c r="P123" s="7"/>
+      <c r="Q123" s="7"/>
+      <c r="R123" s="7"/>
+      <c r="S123" s="7"/>
+      <c r="T123" s="7"/>
+      <c r="U123" s="8"/>
+      <c r="V123" s="2"/>
+      <c r="W123" s="9"/>
     </row>
     <row r="124" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W124" s="7"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="7"/>
+      <c r="K124" s="7"/>
+      <c r="L124" s="7"/>
+      <c r="M124" s="7"/>
+      <c r="N124" s="7"/>
+      <c r="O124" s="7"/>
+      <c r="P124" s="7"/>
+      <c r="Q124" s="7"/>
+      <c r="R124" s="7"/>
+      <c r="S124" s="7"/>
+      <c r="T124" s="7"/>
+      <c r="U124" s="8"/>
+      <c r="V124" s="2"/>
+      <c r="W124" s="9"/>
     </row>
     <row r="125" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W125" s="7"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7"/>
+      <c r="M125" s="7"/>
+      <c r="N125" s="7"/>
+      <c r="O125" s="7"/>
+      <c r="P125" s="7"/>
+      <c r="Q125" s="7"/>
+      <c r="R125" s="7"/>
+      <c r="S125" s="7"/>
+      <c r="T125" s="7"/>
+      <c r="U125" s="8"/>
+      <c r="V125" s="2"/>
+      <c r="W125" s="9"/>
     </row>
     <row r="126" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W126" s="7"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="7"/>
+      <c r="K126" s="7"/>
+      <c r="L126" s="7"/>
+      <c r="M126" s="7"/>
+      <c r="N126" s="7"/>
+      <c r="O126" s="7"/>
+      <c r="P126" s="7"/>
+      <c r="Q126" s="7"/>
+      <c r="R126" s="7"/>
+      <c r="S126" s="7"/>
+      <c r="T126" s="7"/>
+      <c r="U126" s="8"/>
+      <c r="V126" s="2"/>
+      <c r="W126" s="9"/>
     </row>
     <row r="127" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W127" s="7"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="7"/>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7"/>
+      <c r="M127" s="7"/>
+      <c r="N127" s="7"/>
+      <c r="O127" s="7"/>
+      <c r="P127" s="7"/>
+      <c r="Q127" s="7"/>
+      <c r="R127" s="7"/>
+      <c r="S127" s="7"/>
+      <c r="T127" s="7"/>
+      <c r="U127" s="8"/>
+      <c r="V127" s="2"/>
+      <c r="W127" s="9"/>
     </row>
     <row r="128" spans="6:23" x14ac:dyDescent="0.35">
-      <c r="W128" s="7"/>
-    </row>
-    <row r="129" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W129" s="7"/>
-    </row>
-    <row r="130" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W130" s="7"/>
-    </row>
-    <row r="131" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W131" s="7"/>
-    </row>
-    <row r="132" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W132" s="7"/>
-    </row>
-    <row r="133" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W133" s="7"/>
-    </row>
-    <row r="134" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W134" s="7"/>
-    </row>
-    <row r="135" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W135" s="7"/>
-    </row>
-    <row r="136" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W136" s="7"/>
-    </row>
-    <row r="137" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W137" s="7"/>
-    </row>
-    <row r="138" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W138" s="7"/>
-    </row>
-    <row r="139" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W139" s="7"/>
-    </row>
-    <row r="140" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W140" s="7"/>
-    </row>
-    <row r="141" spans="23:23" x14ac:dyDescent="0.35">
-      <c r="W141" s="7"/>
-    </row>
-    <row r="142" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="7"/>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7"/>
+      <c r="M128" s="7"/>
+      <c r="N128" s="7"/>
+      <c r="O128" s="7"/>
+      <c r="P128" s="7"/>
+      <c r="Q128" s="7"/>
+      <c r="R128" s="7"/>
+      <c r="S128" s="7"/>
+      <c r="T128" s="7"/>
+      <c r="U128" s="8"/>
+      <c r="V128" s="2"/>
+      <c r="W128" s="9"/>
+    </row>
+    <row r="129" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="7"/>
+      <c r="K129" s="7"/>
+      <c r="L129" s="7"/>
+      <c r="M129" s="7"/>
+      <c r="N129" s="7"/>
+      <c r="O129" s="7"/>
+      <c r="P129" s="7"/>
+      <c r="Q129" s="7"/>
+      <c r="R129" s="7"/>
+      <c r="S129" s="7"/>
+      <c r="T129" s="7"/>
+      <c r="U129" s="8"/>
+      <c r="V129" s="2"/>
+      <c r="W129" s="9"/>
+    </row>
+    <row r="130" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="7"/>
+      <c r="K130" s="7"/>
+      <c r="L130" s="7"/>
+      <c r="M130" s="7"/>
+      <c r="N130" s="7"/>
+      <c r="O130" s="7"/>
+      <c r="P130" s="7"/>
+      <c r="Q130" s="7"/>
+      <c r="R130" s="7"/>
+      <c r="S130" s="7"/>
+      <c r="T130" s="7"/>
+      <c r="U130" s="8"/>
+      <c r="V130" s="2"/>
+      <c r="W130" s="9"/>
+    </row>
+    <row r="131" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="6"/>
+      <c r="J131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
+      <c r="M131" s="7"/>
+      <c r="N131" s="7"/>
+      <c r="O131" s="7"/>
+      <c r="P131" s="7"/>
+      <c r="Q131" s="7"/>
+      <c r="R131" s="7"/>
+      <c r="S131" s="7"/>
+      <c r="T131" s="7"/>
+      <c r="U131" s="8"/>
+      <c r="V131" s="2"/>
+      <c r="W131" s="9"/>
+    </row>
+    <row r="132" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="7"/>
+      <c r="K132" s="7"/>
+      <c r="L132" s="7"/>
+      <c r="M132" s="7"/>
+      <c r="N132" s="7"/>
+      <c r="O132" s="7"/>
+      <c r="P132" s="7"/>
+      <c r="Q132" s="7"/>
+      <c r="R132" s="7"/>
+      <c r="S132" s="7"/>
+      <c r="T132" s="7"/>
+      <c r="U132" s="8"/>
+      <c r="V132" s="2"/>
+      <c r="W132" s="9"/>
+    </row>
+    <row r="133" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="7"/>
+      <c r="K133" s="7"/>
+      <c r="L133" s="7"/>
+      <c r="M133" s="7"/>
+      <c r="N133" s="7"/>
+      <c r="O133" s="7"/>
+      <c r="P133" s="7"/>
+      <c r="Q133" s="7"/>
+      <c r="R133" s="7"/>
+      <c r="S133" s="7"/>
+      <c r="T133" s="7"/>
+      <c r="U133" s="8"/>
+      <c r="V133" s="2"/>
+      <c r="W133" s="9"/>
+    </row>
+    <row r="134" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="7"/>
+      <c r="K134" s="7"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="7"/>
+      <c r="N134" s="7"/>
+      <c r="O134" s="7"/>
+      <c r="P134" s="7"/>
+      <c r="Q134" s="7"/>
+      <c r="R134" s="7"/>
+      <c r="S134" s="7"/>
+      <c r="T134" s="7"/>
+      <c r="U134" s="8"/>
+      <c r="V134" s="2"/>
+      <c r="W134" s="9"/>
+    </row>
+    <row r="135" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="7"/>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7"/>
+      <c r="M135" s="7"/>
+      <c r="N135" s="7"/>
+      <c r="O135" s="7"/>
+      <c r="P135" s="7"/>
+      <c r="Q135" s="7"/>
+      <c r="R135" s="7"/>
+      <c r="S135" s="7"/>
+      <c r="T135" s="7"/>
+      <c r="U135" s="8"/>
+      <c r="V135" s="2"/>
+      <c r="W135" s="9"/>
+    </row>
+    <row r="136" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="7"/>
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
+      <c r="N136" s="7"/>
+      <c r="O136" s="7"/>
+      <c r="P136" s="7"/>
+      <c r="Q136" s="7"/>
+      <c r="R136" s="7"/>
+      <c r="S136" s="7"/>
+      <c r="T136" s="7"/>
+      <c r="U136" s="8"/>
+      <c r="V136" s="2"/>
+      <c r="W136" s="9"/>
+    </row>
+    <row r="137" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="7"/>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="7"/>
+      <c r="N137" s="7"/>
+      <c r="O137" s="7"/>
+      <c r="P137" s="7"/>
+      <c r="Q137" s="7"/>
+      <c r="R137" s="7"/>
+      <c r="S137" s="7"/>
+      <c r="T137" s="7"/>
+      <c r="U137" s="8"/>
+      <c r="V137" s="2"/>
+      <c r="W137" s="9"/>
+    </row>
+    <row r="138" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7"/>
+      <c r="N138" s="7"/>
+      <c r="O138" s="7"/>
+      <c r="P138" s="7"/>
+      <c r="Q138" s="7"/>
+      <c r="R138" s="7"/>
+      <c r="S138" s="7"/>
+      <c r="T138" s="7"/>
+      <c r="U138" s="8"/>
+      <c r="V138" s="2"/>
+      <c r="W138" s="9"/>
+    </row>
+    <row r="139" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="7"/>
+      <c r="K139" s="7"/>
+      <c r="L139" s="7"/>
+      <c r="M139" s="7"/>
+      <c r="N139" s="7"/>
+      <c r="O139" s="7"/>
+      <c r="P139" s="7"/>
+      <c r="Q139" s="7"/>
+      <c r="R139" s="7"/>
+      <c r="S139" s="7"/>
+      <c r="T139" s="7"/>
+      <c r="U139" s="8"/>
+      <c r="V139" s="2"/>
+      <c r="W139" s="9"/>
+    </row>
+    <row r="140" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="7"/>
+      <c r="K140" s="7"/>
+      <c r="L140" s="7"/>
+      <c r="M140" s="7"/>
+      <c r="N140" s="7"/>
+      <c r="O140" s="7"/>
+      <c r="P140" s="7"/>
+      <c r="Q140" s="7"/>
+      <c r="R140" s="7"/>
+      <c r="S140" s="7"/>
+      <c r="T140" s="7"/>
+      <c r="U140" s="8"/>
+      <c r="V140" s="2"/>
+      <c r="W140" s="9"/>
+    </row>
+    <row r="141" spans="6:23" x14ac:dyDescent="0.35">
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="7"/>
+      <c r="L141" s="7"/>
+      <c r="M141" s="7"/>
+      <c r="N141" s="7"/>
+      <c r="O141" s="7"/>
+      <c r="P141" s="7"/>
+      <c r="Q141" s="7"/>
+      <c r="R141" s="7"/>
+      <c r="S141" s="7"/>
+      <c r="T141" s="7"/>
+      <c r="U141" s="8"/>
+      <c r="V141" s="2"/>
+      <c r="W141" s="9"/>
+    </row>
+    <row r="142" spans="6:23" x14ac:dyDescent="0.35">
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="143" spans="6:23" x14ac:dyDescent="0.35">
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="23:23" x14ac:dyDescent="0.35">
+    <row r="144" spans="6:23" x14ac:dyDescent="0.35">
       <c r="W144" s="7"/>
     </row>
     <row r="145" spans="23:23" x14ac:dyDescent="0.35">
@@ -7248,8 +8468,77 @@
     <row r="535" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W535" s="7"/>
     </row>
+    <row r="536" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W536" s="7"/>
+    </row>
+    <row r="537" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W537" s="7"/>
+    </row>
+    <row r="538" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W538" s="7"/>
+    </row>
+    <row r="539" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W539" s="7"/>
+    </row>
+    <row r="540" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W540" s="7"/>
+    </row>
+    <row r="541" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W541" s="7"/>
+    </row>
+    <row r="542" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W542" s="7"/>
+    </row>
+    <row r="543" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W543" s="7"/>
+    </row>
+    <row r="544" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W544" s="7"/>
+    </row>
+    <row r="545" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W545" s="7"/>
+    </row>
+    <row r="546" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W546" s="7"/>
+    </row>
+    <row r="547" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W547" s="7"/>
+    </row>
+    <row r="548" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W548" s="7"/>
+    </row>
+    <row r="549" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W549" s="7"/>
+    </row>
+    <row r="550" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W550" s="7"/>
+    </row>
+    <row r="551" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W551" s="7"/>
+    </row>
+    <row r="552" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W552" s="7"/>
+    </row>
+    <row r="553" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W553" s="7"/>
+    </row>
+    <row r="554" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W554" s="7"/>
+    </row>
+    <row r="555" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W555" s="7"/>
+    </row>
+    <row r="556" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W556" s="7"/>
+    </row>
+    <row r="557" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W557" s="7"/>
+    </row>
+    <row r="558" spans="23:23" x14ac:dyDescent="0.35">
+      <c r="W558" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:W32" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:W55" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -7270,19 +8559,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M21:N32 P21:R32 J11:J32 P10:R19 M11:N19</xm:sqref>
+          <xm:sqref>P16:R22 M37:N55 M11:N22 J16:J40 P37:R55 J42 P10:R10 P12:R12 J11:J14 P14:R14 M24:N35 P24:R35 J44:J55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T32</xm:sqref>
+          <xm:sqref>T10:T55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K32</xm:sqref>
+          <xm:sqref>K10:K40 K42 K44:K55</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7297,42 +8586,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -7356,22 +8645,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="G1" s="40" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7379,13 +8668,13 @@
         <v>44</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7393,13 +8682,13 @@
         <v>48</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7407,55 +8696,55 @@
         <v>50</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -7463,13 +8752,13 @@
         <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -7477,97 +8766,97 @@
         <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C15" s="12">
         <v>521</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>147</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -8542,18 +9831,18 @@
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9567,15 +10856,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
@@ -9585,6 +10865,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9852,14 +11141,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
@@ -9872,6 +11153,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
